--- a/data/trans_orig/LAWTONB_2R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>47342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62269</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31771</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42640</t>
+          <t>42043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66104</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82662</t>
+          <t>83700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114619</t>
+          <t>114397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136373</t>
+          <t>136649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45534</t>
+          <t>44955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>35962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57750</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>38566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>56879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97979</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58687</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>46193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>33235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>50599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70749</t>
+          <t>70474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91372</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +2155,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>52,57%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>24257</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>17052</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>32903</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>24,16%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>54,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>24257</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>16494</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>31378</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>46336</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>37690</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>53541</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>65,64%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>53,39%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>75,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>46336</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>39215</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>54099</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>55,55%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57815</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35090</t>
+          <t>35092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50659</t>
+          <t>50310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59691</t>
+          <t>61300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81754</t>
+          <t>81789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50865</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46481</t>
+          <t>45908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>71921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77109</t>
+          <t>78274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66256</t>
+          <t>67668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87410</t>
+          <t>87558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>149999</t>
+          <t>151128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>176568</t>
+          <t>177141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26426</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46028</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70182</t>
+          <t>69857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65865</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85467</t>
+          <t>84691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92295</t>
+          <t>92177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116007</t>
+          <t>116489</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>164532</t>
+          <t>164887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>194936</t>
+          <t>195261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114697</t>
+          <t>115143</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151761</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>209951</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>260274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>330432</t>
+          <t>332744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>350705</t>
+          <t>349507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>387769</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>784114</t>
+          <t>783585</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>848876</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34403</t>
+          <t>33856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54685</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58772</t>
+          <t>59319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54417</t>
+          <t>53655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53728</t>
+          <t>54217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>81377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64141</t>
+          <t>63920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>48438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>99919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127568</t>
+          <t>127079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34997</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,47 +4792,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>40891</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>30702</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>53426</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>22,62%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>40891</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>29874</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51532</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>22,01%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33484</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>44408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>61297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,47 +4905,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>94819</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>82284</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>105008</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>77,38%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>94819</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>84178</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>105836</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>62,03%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49486</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>49955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74263</t>
+          <t>74033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49578</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>35884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54186</t>
+          <t>54510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75339</t>
+          <t>75569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100200</t>
+          <t>99647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>43550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56491</t>
+          <t>55606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49680</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>40628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>72214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92218</t>
+          <t>92243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39572</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94235</t>
+          <t>95327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72691</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92378</t>
+          <t>92309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80641</t>
+          <t>79712</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>103121</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159991</t>
+          <t>158899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190337</t>
+          <t>190686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>38834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>62961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57079</t>
+          <t>56567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86892</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89717</t>
+          <t>89123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108764</t>
+          <t>107457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100071</t>
+          <t>101456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125158</t>
+          <t>125583</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198277</t>
+          <t>197866</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>228090</t>
+          <t>228602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>127667</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>172407</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261377</t>
+          <t>260717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>315014</t>
+          <t>316377</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400951</t>
+          <t>400732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>471055</t>
+          <t>470735</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>427961</t>
+          <t>426598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>481598</t>
+          <t>482258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>831557</t>
+          <t>831877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>901661</t>
+          <t>901880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>44893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>61870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>40753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65857</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79534</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64618</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87500</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>134276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162894</t>
+          <t>161770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43970</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>41697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>54559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53302</t>
+          <t>53012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69734</t>
+          <t>69536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>101094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120692</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>56979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71605</t>
+          <t>71371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100420</t>
+          <t>99306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124073</t>
+          <t>122756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>21248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>39406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32727</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53322</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71926</t>
+          <t>71364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48591</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35515</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52731</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67243</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75130</t>
+          <t>74626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73918</t>
+          <t>74993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106120</t>
+          <t>106663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75036</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>93202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72495</t>
+          <t>72999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>99354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153690</t>
+          <t>153147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185892</t>
+          <t>184817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43064</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73067</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>65618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98852</t>
+          <t>98329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>99559</t>
+          <t>100209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116373</t>
+          <t>117347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103230</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>211613</t>
+          <t>212136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244104</t>
+          <t>244847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106103</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>142797</t>
+          <t>143942</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>247689</t>
+          <t>251097</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>304264</t>
+          <t>306449</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>370897</t>
+          <t>367801</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>440086</t>
+          <t>438824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>448531</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>485225</t>
+          <t>485687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>473667</t>
+          <t>471482</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>530242</t>
+          <t>526834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>929173</t>
+          <t>930435</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>998362</t>
+          <t>1001458</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38766</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>52642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69730</t>
+          <t>69633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>49677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>49098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66288</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62760</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84441</t>
+          <t>84952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>56221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69739</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>63064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79659</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123874</t>
+          <t>123363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145555</t>
+          <t>145378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>51868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62415</t>
+          <t>62407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80783</t>
+          <t>81921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53368</t>
+          <t>52395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>34991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48698</t>
+          <t>49069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79566</t>
+          <t>78428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97934</t>
+          <t>97942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>30503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>43546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45182</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61603</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49956</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60959</t>
+          <t>60825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>60090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>73133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114961</t>
+          <t>115012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131382</t>
+          <t>131459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>21660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28932</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>61451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>72642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18999</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50192</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64202</t>
+          <t>64462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>31312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74531</t>
+          <t>74415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140544</t>
+          <t>140778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24376</t>
+          <t>25802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142316</t>
+          <t>142109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>91246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106924</t>
+          <t>106390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>197015</t>
+          <t>196781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>322219</t>
+          <t>325645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317781</t>
+          <t>317988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>435721</t>
+          <t>434295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>56828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75642</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74287</t>
+          <t>73580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97653</t>
+          <t>97921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>117034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130909</t>
+          <t>130718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129819</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232905</t>
+          <t>232637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>256271</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145980</t>
+          <t>145589</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>181314</t>
+          <t>180902</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178478</t>
+          <t>179236</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>434506</t>
+          <t>433745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>352520</t>
+          <t>344724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>586783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>463090</t>
+          <t>463502</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498424</t>
+          <t>498815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>594718</t>
+          <t>595479</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>849988</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1089502</t>
+          <t>1086845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1321108</t>
+          <t>1328904</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>30888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>47580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62299</t>
+          <t>62060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24611</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>32239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42043</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56511</t>
+          <t>56799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83700</t>
+          <t>82626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114397</t>
+          <t>113747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>135538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>57168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>45347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56879</t>
+          <t>56046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77772</t>
+          <t>77293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>98060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23714</t>
+          <t>24184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33235</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50599</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>69853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91743</t>
+          <t>91162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>22301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>36328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>56353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34069</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50310</t>
+          <t>50749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61300</t>
+          <t>61153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81789</t>
+          <t>81979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>45906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>73118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78274</t>
+          <t>78064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>92765</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67668</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87558</t>
+          <t>87648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>151128</t>
+          <t>149931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177141</t>
+          <t>177143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>44983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69857</t>
+          <t>70863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100231</t>
+          <t>101420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66315</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84691</t>
+          <t>85800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92177</t>
+          <t>92993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116489</t>
+          <t>115370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>164887</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195261</t>
+          <t>194255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115143</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209277</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>260274</t>
+          <t>259970</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>332744</t>
+          <t>334693</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>395723</t>
+          <t>394645</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>36911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33856</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54197</t>
+          <t>53947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>59429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53655</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54217</t>
+          <t>54181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81377</t>
+          <t>82643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>45414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63920</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69070</t>
+          <t>68354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>98653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127079</t>
+          <t>127115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30702</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>33390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47418</t>
+          <t>47336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44408</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61297</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82284</t>
+          <t>82993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105008</t>
+          <t>104996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49690</t>
+          <t>49889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74033</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>54052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75569</t>
+          <t>75933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99647</t>
+          <t>100990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32382</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43550</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>27246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40628</t>
+          <t>41243</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56222</t>
+          <t>56257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72214</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92243</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19954</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40409</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>37314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>63629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95327</t>
+          <t>95399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71854</t>
+          <t>71696</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92309</t>
+          <t>91396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79712</t>
+          <t>81234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103121</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>158899</t>
+          <t>158827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190686</t>
+          <t>190597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>31778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62961</t>
+          <t>63096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>55357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87303</t>
+          <t>85964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107457</t>
+          <t>107683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>101321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125583</t>
+          <t>126070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197866</t>
+          <t>199205</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>228602</t>
+          <t>229812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>260717</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316377</t>
+          <t>313752</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400732</t>
+          <t>400904</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>470735</t>
+          <t>469767</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>426598</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>482258</t>
+          <t>484289</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>831877</t>
+          <t>832845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>901880</t>
+          <t>901708</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31398</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61870</t>
+          <t>62663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>51544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>65691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66194</t>
+          <t>66075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>79120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64845</t>
+          <t>63684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>87011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134276</t>
+          <t>136832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161770</t>
+          <t>162268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41697</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>54093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69536</t>
+          <t>69269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101094</t>
+          <t>98825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>120819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56979</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>42240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55560</t>
+          <t>54907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71371</t>
+          <t>71529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>99019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122756</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>31993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53206</t>
+          <t>54119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71364</t>
+          <t>72701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>49518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>38603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>66316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>87361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48271</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74626</t>
+          <t>73794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74993</t>
+          <t>72795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106663</t>
+          <t>105443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93202</t>
+          <t>92317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72999</t>
+          <t>73831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99354</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153147</t>
+          <t>154367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>184817</t>
+          <t>187015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>44051</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>71045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65618</t>
+          <t>63951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98329</t>
+          <t>98931</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>100209</t>
+          <t>99369</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117347</t>
+          <t>116943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105367</t>
+          <t>105252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132745</t>
+          <t>132246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>212136</t>
+          <t>211534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244847</t>
+          <t>246514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>143942</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>248112</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>306449</t>
+          <t>305455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>367801</t>
+          <t>364334</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>438824</t>
+          <t>433164</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>526834</t>
+          <t>529819</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>930435</t>
+          <t>936095</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1001458</t>
+          <t>1004925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33314</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39157</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>63927</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52642</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69633</t>
+          <t>72444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>24318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34110</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>31251</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58236</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49677</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>60938</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49098</t>
+          <t>52195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73497</t>
+          <t>78330</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>66747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84952</t>
+          <t>90720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63657</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71161</t>
+          <t>73821</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>82564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134818</t>
+          <t>143873</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123363</t>
+          <t>131483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145378</t>
+          <t>155456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33616</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44891</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>38919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>52149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62407</t>
+          <t>62087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81921</t>
+          <t>81130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>45894</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49069</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>86226</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78428</t>
+          <t>76436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97942</t>
+          <t>95479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>24623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>31928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>48261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61552</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55807</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60825</t>
+          <t>68655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>71985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>123033</t>
+          <t>135031</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115012</t>
+          <t>125280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131459</t>
+          <t>143635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17268</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>46975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72642</t>
+          <t>76291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57166</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50308</t>
+          <t>51095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>65152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>37941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>67557</t>
+          <t>68838</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>61546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74415</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>27845</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>64076</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140778</t>
+          <t>74226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>75016</t>
+          <t>91921</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>78717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142109</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>99936</t>
+          <t>122686</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91246</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>131216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>285146</t>
+          <t>98821</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196781</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325645</t>
+          <t>108569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>385081</t>
+          <t>221507</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317988</t>
+          <t>207037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>434295</t>
+          <t>234711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>76484</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56828</t>
+          <t>66104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75704</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>85588</t>
+          <t>98774</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>85774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97921</t>
+          <t>113088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>125168</t>
+          <t>138583</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117034</t>
+          <t>130506</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130718</t>
+          <t>145105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>119802</t>
+          <t>135378</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110235</t>
+          <t>124231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129111</t>
+          <t>145758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>273961</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232637</t>
+          <t>259647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>286961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145589</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>180902</t>
+          <t>197033</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>179236</t>
+          <t>348962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>433745</t>
+          <t>390260</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>517575</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>586783</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>481399</t>
+          <t>534750</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>463502</t>
+          <t>513174</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498815</t>
+          <t>551253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>507958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>849988</t>
+          <t>549256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1169736</t>
+          <t>1062206</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1031392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1328904</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
